--- a/artfynd/A 33994-2026 artfynd.xlsx
+++ b/artfynd/A 33994-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113680121</v>
+        <v>136100389</v>
       </c>
       <c r="B2" t="n">
-        <v>93287</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Erik-Pettersudden, Jmt</t>
+          <t>Avverkning Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505068</v>
+        <v>504932</v>
       </c>
       <c r="R2" t="n">
-        <v>7131318</v>
+        <v>7131301</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,73 +773,64 @@
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>Kristofer Wester</t>
-        </is>
-      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristofer Wester</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113680121</t>
+          <t>https://artportalen.se/Sighting/136100389</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113680120</v>
+        <v>136100396</v>
       </c>
       <c r="B3" t="n">
-        <v>93271</v>
+        <v>92310</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Erik-Pettersudden, Jmt</t>
+          <t>Avverkning Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504991</v>
+        <v>504990</v>
       </c>
       <c r="R3" t="n">
-        <v>7131271</v>
+        <v>7131251</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,47 +857,7032 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100396</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136100403</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92310</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>65</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläckporing</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Anthoporia albobrunnea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>505027</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7131274</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100403</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136100351</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79109</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>353</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>504632</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7131348</v>
+      </c>
+      <c r="S5" t="n">
+        <v>17</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100351</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136100353</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79109</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>353</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>504655</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7131346</v>
+      </c>
+      <c r="S6" t="n">
+        <v>7</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100353</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136100361</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79109</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>353</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>504676</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7131413</v>
+      </c>
+      <c r="S7" t="n">
+        <v>16</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100361</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136100408</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79109</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>353</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>504820</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7131355</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100408</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136100377</v>
+      </c>
+      <c r="B9" t="n">
+        <v>81425</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>504808</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7131442</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100377</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136100363</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92243</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>504733</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7131392</v>
+      </c>
+      <c r="S10" t="n">
+        <v>23</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100363</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136100375</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92243</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>504796</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7131435</v>
+      </c>
+      <c r="S11" t="n">
+        <v>8</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100375</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136100400</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92243</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>505071</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7131290</v>
+      </c>
+      <c r="S12" t="n">
+        <v>14</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100400</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136100402</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92243</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>505084</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7131302</v>
+      </c>
+      <c r="S13" t="n">
+        <v>33</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100402</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136100365</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92417</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ostticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Skeletocutis odora</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>504738</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7131384</v>
+      </c>
+      <c r="S14" t="n">
+        <v>11</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100365</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136100349</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91073</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>504641</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7131299</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100349</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136100358</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91073</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>504658</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7131401</v>
+      </c>
+      <c r="S16" t="n">
+        <v>8</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100358</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>113680121</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93287</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Erik-Pettersudden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>505068</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7131318</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
           <t>2023-10-03</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>2023-10-03</t>
         </is>
       </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr">
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr">
         <is>
           <t>Kristofer Wester</t>
         </is>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="AW17" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Kristofer Wester</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY17" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680121</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136100354</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92117</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>504661</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7131346</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100354</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136100362</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92117</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>504707</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7131391</v>
+      </c>
+      <c r="S19" t="n">
+        <v>19</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100362</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136100366</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93282</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3382</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Aspskinn</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Conferticium ravum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Burt) Ginns &amp; G.W. Freeman</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>504738</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7131384</v>
+      </c>
+      <c r="S20" t="n">
+        <v>6</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100366</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>113680120</v>
+      </c>
+      <c r="B21" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Erik-Pettersudden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>504991</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7131271</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/113680120</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136100350</v>
+      </c>
+      <c r="B22" t="n">
+        <v>93362</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>504627</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7131346</v>
+      </c>
+      <c r="S22" t="n">
+        <v>21</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100350</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136100357</v>
+      </c>
+      <c r="B23" t="n">
+        <v>93362</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>504669</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7131400</v>
+      </c>
+      <c r="S23" t="n">
+        <v>16</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100357</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136100360</v>
+      </c>
+      <c r="B24" t="n">
+        <v>93362</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>504668</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7131401</v>
+      </c>
+      <c r="S24" t="n">
+        <v>11</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100360</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136100370</v>
+      </c>
+      <c r="B25" t="n">
+        <v>93362</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>504722</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7131434</v>
+      </c>
+      <c r="S25" t="n">
+        <v>24</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100370</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136100371</v>
+      </c>
+      <c r="B26" t="n">
+        <v>93362</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>504715</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7131448</v>
+      </c>
+      <c r="S26" t="n">
+        <v>7</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100371</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136100407</v>
+      </c>
+      <c r="B27" t="n">
+        <v>93362</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>504844</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7131376</v>
+      </c>
+      <c r="S27" t="n">
+        <v>9</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100407</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136100355</v>
+      </c>
+      <c r="B28" t="n">
+        <v>93366</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>504669</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7131389</v>
+      </c>
+      <c r="S28" t="n">
+        <v>18</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100355</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136100356</v>
+      </c>
+      <c r="B29" t="n">
+        <v>93366</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>504667</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7131392</v>
+      </c>
+      <c r="S29" t="n">
+        <v>24</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100356</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136100372</v>
+      </c>
+      <c r="B30" t="n">
+        <v>93366</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>504729</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7131450</v>
+      </c>
+      <c r="S30" t="n">
+        <v>17</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100372</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136100378</v>
+      </c>
+      <c r="B31" t="n">
+        <v>93366</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>504814</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7131447</v>
+      </c>
+      <c r="S31" t="n">
+        <v>19</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100378</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136100368</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>504748</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7131392</v>
+      </c>
+      <c r="S32" t="n">
+        <v>19</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100368</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136100390</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79467</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>504979</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7131252</v>
+      </c>
+      <c r="S33" t="n">
+        <v>6</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100390</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136100344</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78846</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>504673</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7131297</v>
+      </c>
+      <c r="S34" t="n">
+        <v>9</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100344</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136100374</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78846</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>504782</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7131463</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100374</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136100380</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78846</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>504833</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7131421</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100380</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136100383</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78846</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>504902</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7131374</v>
+      </c>
+      <c r="S37" t="n">
+        <v>13</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100383</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>136100399</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78846</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>505037</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7131268</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100399</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>136100411</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79200</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>504722</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7131315</v>
+      </c>
+      <c r="S39" t="n">
+        <v>16</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100411</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>136100343</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80062</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>504674</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7131287</v>
+      </c>
+      <c r="S40" t="n">
+        <v>21</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100343</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136100347</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80062</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>504658</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7131295</v>
+      </c>
+      <c r="S41" t="n">
+        <v>14</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100347</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>136100352</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80062</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>504630</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7131347</v>
+      </c>
+      <c r="S42" t="n">
+        <v>17</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100352</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>136100364</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80569</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>504741</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7131383</v>
+      </c>
+      <c r="S43" t="n">
+        <v>19</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100364</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>136100345</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78447</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>504673</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7131306</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100345</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>136100391</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78447</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>504978</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7131251</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100391</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>136100384</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57169</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>504913</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7131326</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100384</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>136100386</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>504924</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7131309</v>
+      </c>
+      <c r="S47" t="n">
+        <v>14</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Minst 3000st</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100386</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>136100388</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>504930</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7131306</v>
+      </c>
+      <c r="S48" t="n">
+        <v>17</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100388</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>136100406</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>504925</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7131326</v>
+      </c>
+      <c r="S49" t="n">
+        <v>7</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100406</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>136100376</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79201</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>504797</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7131437</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100376</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>136100381</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79201</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>504902</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7131371</v>
+      </c>
+      <c r="S51" t="n">
+        <v>31</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100381</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>136100385</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79201</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>504909</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7131325</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100385</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>136100394</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79201</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>504978</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7131251</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100394</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>136100397</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79201</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>505034</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7131284</v>
+      </c>
+      <c r="S54" t="n">
+        <v>11</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100397</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>136100409</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79201</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>504808</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7131365</v>
+      </c>
+      <c r="S55" t="n">
+        <v>21</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100409</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>136100412</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79201</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>504722</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7131315</v>
+      </c>
+      <c r="S56" t="n">
+        <v>16</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100412</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>136100346</v>
+      </c>
+      <c r="B57" t="n">
+        <v>80033</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>504676</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7131308</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100346</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>136100348</v>
+      </c>
+      <c r="B58" t="n">
+        <v>80033</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>504659</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7131296</v>
+      </c>
+      <c r="S58" t="n">
+        <v>14</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100348</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>136100373</v>
+      </c>
+      <c r="B59" t="n">
+        <v>80033</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>504780</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7131456</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100373</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>136100379</v>
+      </c>
+      <c r="B60" t="n">
+        <v>80033</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>504817</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7131447</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100379</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>136100382</v>
+      </c>
+      <c r="B61" t="n">
+        <v>80033</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>504902</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7131371</v>
+      </c>
+      <c r="S61" t="n">
+        <v>21</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100382</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>136100393</v>
+      </c>
+      <c r="B62" t="n">
+        <v>80033</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>504978</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7131251</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100393</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>136100398</v>
+      </c>
+      <c r="B63" t="n">
+        <v>80033</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>505037</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7131268</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100398</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>136100413</v>
+      </c>
+      <c r="B64" t="n">
+        <v>80033</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>504722</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7131315</v>
+      </c>
+      <c r="S64" t="n">
+        <v>7</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100413</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>136100414</v>
+      </c>
+      <c r="B65" t="n">
+        <v>80033</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Avverkning Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>504718</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7131307</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136100414</t>
         </is>
       </c>
     </row>
@@ -904,6 +7890,68 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33994-2026 artfynd.xlsx
+++ b/artfynd/A 33994-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136100389</v>
       </c>
       <c r="B2" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136100396</v>
       </c>
       <c r="B3" t="n">
-        <v>92310</v>
+        <v>92311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136100403</v>
       </c>
       <c r="B4" t="n">
-        <v>92310</v>
+        <v>92311</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136100351</v>
       </c>
       <c r="B5" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136100353</v>
       </c>
       <c r="B6" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136100361</v>
       </c>
       <c r="B7" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136100408</v>
       </c>
       <c r="B8" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136100377</v>
       </c>
       <c r="B9" t="n">
-        <v>81425</v>
+        <v>81426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136100363</v>
       </c>
       <c r="B10" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136100375</v>
       </c>
       <c r="B11" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136100400</v>
       </c>
       <c r="B12" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136100402</v>
       </c>
       <c r="B13" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136100365</v>
       </c>
       <c r="B14" t="n">
-        <v>92417</v>
+        <v>92418</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136100349</v>
       </c>
       <c r="B15" t="n">
-        <v>91073</v>
+        <v>91074</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136100358</v>
       </c>
       <c r="B16" t="n">
-        <v>91073</v>
+        <v>91074</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>136100354</v>
       </c>
       <c r="B18" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136100362</v>
       </c>
       <c r="B19" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136100366</v>
       </c>
       <c r="B20" t="n">
-        <v>93282</v>
+        <v>93283</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136100350</v>
       </c>
       <c r="B22" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>136100357</v>
       </c>
       <c r="B23" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>136100360</v>
       </c>
       <c r="B24" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136100370</v>
       </c>
       <c r="B25" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>136100371</v>
       </c>
       <c r="B26" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136100407</v>
       </c>
       <c r="B27" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>136100355</v>
       </c>
       <c r="B28" t="n">
-        <v>93366</v>
+        <v>93367</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>136100356</v>
       </c>
       <c r="B29" t="n">
-        <v>93366</v>
+        <v>93367</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>136100372</v>
       </c>
       <c r="B30" t="n">
-        <v>93366</v>
+        <v>93367</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>136100378</v>
       </c>
       <c r="B31" t="n">
-        <v>93366</v>
+        <v>93367</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>136100368</v>
       </c>
       <c r="B32" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>136100390</v>
       </c>
       <c r="B33" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>136100344</v>
       </c>
       <c r="B34" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>136100374</v>
       </c>
       <c r="B35" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>136100380</v>
       </c>
       <c r="B36" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>136100383</v>
       </c>
       <c r="B37" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>136100399</v>
       </c>
       <c r="B38" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>136100411</v>
       </c>
       <c r="B39" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         <v>136100343</v>
       </c>
       <c r="B40" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>136100347</v>
       </c>
       <c r="B41" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>136100352</v>
       </c>
       <c r="B42" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>136100364</v>
       </c>
       <c r="B43" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>136100345</v>
       </c>
       <c r="B44" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>136100391</v>
       </c>
       <c r="B45" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136100386</v>
       </c>
       <c r="B47" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>136100388</v>
       </c>
       <c r="B48" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>136100406</v>
       </c>
       <c r="B49" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>136100376</v>
       </c>
       <c r="B50" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>136100381</v>
       </c>
       <c r="B51" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>136100385</v>
       </c>
       <c r="B52" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>136100394</v>
       </c>
       <c r="B53" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>136100397</v>
       </c>
       <c r="B54" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>136100409</v>
       </c>
       <c r="B55" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>136100412</v>
       </c>
       <c r="B56" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>136100346</v>
       </c>
       <c r="B57" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>136100348</v>
       </c>
       <c r="B58" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>136100373</v>
       </c>
       <c r="B59" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>136100379</v>
       </c>
       <c r="B60" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>136100382</v>
       </c>
       <c r="B61" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>136100393</v>
       </c>
       <c r="B62" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>136100398</v>
       </c>
       <c r="B63" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         <v>136100413</v>
       </c>
       <c r="B64" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>136100414</v>
       </c>
       <c r="B65" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 33994-2026 artfynd.xlsx
+++ b/artfynd/A 33994-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136100389</v>
       </c>
       <c r="B2" t="n">
-        <v>97531</v>
+        <v>97532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136100396</v>
       </c>
       <c r="B3" t="n">
-        <v>92311</v>
+        <v>92312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136100403</v>
       </c>
       <c r="B4" t="n">
-        <v>92311</v>
+        <v>92312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136100363</v>
       </c>
       <c r="B10" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136100375</v>
       </c>
       <c r="B11" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136100400</v>
       </c>
       <c r="B12" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136100402</v>
       </c>
       <c r="B13" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136100365</v>
       </c>
       <c r="B14" t="n">
-        <v>92418</v>
+        <v>92419</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136100349</v>
       </c>
       <c r="B15" t="n">
-        <v>91074</v>
+        <v>91075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136100358</v>
       </c>
       <c r="B16" t="n">
-        <v>91074</v>
+        <v>91075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>136100354</v>
       </c>
       <c r="B18" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136100362</v>
       </c>
       <c r="B19" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136100366</v>
       </c>
       <c r="B20" t="n">
-        <v>93283</v>
+        <v>93284</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136100350</v>
       </c>
       <c r="B22" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>136100357</v>
       </c>
       <c r="B23" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>136100360</v>
       </c>
       <c r="B24" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136100370</v>
       </c>
       <c r="B25" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>136100371</v>
       </c>
       <c r="B26" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136100407</v>
       </c>
       <c r="B27" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>136100355</v>
       </c>
       <c r="B28" t="n">
-        <v>93367</v>
+        <v>93368</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>136100356</v>
       </c>
       <c r="B29" t="n">
-        <v>93367</v>
+        <v>93368</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>136100372</v>
       </c>
       <c r="B30" t="n">
-        <v>93367</v>
+        <v>93368</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>136100378</v>
       </c>
       <c r="B31" t="n">
-        <v>93367</v>
+        <v>93368</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136100386</v>
       </c>
       <c r="B47" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>136100388</v>
       </c>
       <c r="B48" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>136100406</v>
       </c>
       <c r="B49" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 33994-2026 artfynd.xlsx
+++ b/artfynd/A 33994-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136100389</v>
       </c>
       <c r="B2" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136100396</v>
       </c>
       <c r="B3" t="n">
-        <v>92312</v>
+        <v>92313</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136100403</v>
       </c>
       <c r="B4" t="n">
-        <v>92312</v>
+        <v>92313</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136100351</v>
       </c>
       <c r="B5" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136100353</v>
       </c>
       <c r="B6" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136100361</v>
       </c>
       <c r="B7" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136100408</v>
       </c>
       <c r="B8" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136100377</v>
       </c>
       <c r="B9" t="n">
-        <v>81426</v>
+        <v>81427</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136100363</v>
       </c>
       <c r="B10" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136100375</v>
       </c>
       <c r="B11" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136100400</v>
       </c>
       <c r="B12" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136100402</v>
       </c>
       <c r="B13" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136100365</v>
       </c>
       <c r="B14" t="n">
-        <v>92419</v>
+        <v>92420</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136100349</v>
       </c>
       <c r="B15" t="n">
-        <v>91075</v>
+        <v>91076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136100358</v>
       </c>
       <c r="B16" t="n">
-        <v>91075</v>
+        <v>91076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>136100354</v>
       </c>
       <c r="B18" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136100362</v>
       </c>
       <c r="B19" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136100366</v>
       </c>
       <c r="B20" t="n">
-        <v>93284</v>
+        <v>93285</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136100350</v>
       </c>
       <c r="B22" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>136100357</v>
       </c>
       <c r="B23" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>136100360</v>
       </c>
       <c r="B24" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136100370</v>
       </c>
       <c r="B25" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>136100371</v>
       </c>
       <c r="B26" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136100407</v>
       </c>
       <c r="B27" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>136100355</v>
       </c>
       <c r="B28" t="n">
-        <v>93368</v>
+        <v>93369</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>136100356</v>
       </c>
       <c r="B29" t="n">
-        <v>93368</v>
+        <v>93369</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>136100372</v>
       </c>
       <c r="B30" t="n">
-        <v>93368</v>
+        <v>93369</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>136100378</v>
       </c>
       <c r="B31" t="n">
-        <v>93368</v>
+        <v>93369</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>136100368</v>
       </c>
       <c r="B32" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>136100390</v>
       </c>
       <c r="B33" t="n">
-        <v>79468</v>
+        <v>79469</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>136100344</v>
       </c>
       <c r="B34" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>136100374</v>
       </c>
       <c r="B35" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>136100380</v>
       </c>
       <c r="B36" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>136100383</v>
       </c>
       <c r="B37" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>136100399</v>
       </c>
       <c r="B38" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>136100411</v>
       </c>
       <c r="B39" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         <v>136100343</v>
       </c>
       <c r="B40" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>136100347</v>
       </c>
       <c r="B41" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>136100352</v>
       </c>
       <c r="B42" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>136100364</v>
       </c>
       <c r="B43" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>136100345</v>
       </c>
       <c r="B44" t="n">
-        <v>78448</v>
+        <v>78449</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>136100391</v>
       </c>
       <c r="B45" t="n">
-        <v>78448</v>
+        <v>78449</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>136100384</v>
       </c>
       <c r="B46" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136100386</v>
       </c>
       <c r="B47" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>136100388</v>
       </c>
       <c r="B48" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>136100406</v>
       </c>
       <c r="B49" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>136100376</v>
       </c>
       <c r="B50" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>136100381</v>
       </c>
       <c r="B51" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>136100385</v>
       </c>
       <c r="B52" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>136100394</v>
       </c>
       <c r="B53" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>136100397</v>
       </c>
       <c r="B54" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>136100409</v>
       </c>
       <c r="B55" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>136100412</v>
       </c>
       <c r="B56" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>136100346</v>
       </c>
       <c r="B57" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>136100348</v>
       </c>
       <c r="B58" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>136100373</v>
       </c>
       <c r="B59" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>136100379</v>
       </c>
       <c r="B60" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>136100382</v>
       </c>
       <c r="B61" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>136100393</v>
       </c>
       <c r="B62" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>136100398</v>
       </c>
       <c r="B63" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         <v>136100413</v>
       </c>
       <c r="B64" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>136100414</v>
       </c>
       <c r="B65" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 33994-2026 artfynd.xlsx
+++ b/artfynd/A 33994-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136100389</v>
       </c>
       <c r="B2" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136100396</v>
       </c>
       <c r="B3" t="n">
-        <v>92313</v>
+        <v>92319</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136100403</v>
       </c>
       <c r="B4" t="n">
-        <v>92313</v>
+        <v>92319</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136100351</v>
       </c>
       <c r="B5" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136100353</v>
       </c>
       <c r="B6" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136100361</v>
       </c>
       <c r="B7" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136100408</v>
       </c>
       <c r="B8" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136100377</v>
       </c>
       <c r="B9" t="n">
-        <v>81427</v>
+        <v>81431</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136100363</v>
       </c>
       <c r="B10" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136100375</v>
       </c>
       <c r="B11" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136100400</v>
       </c>
       <c r="B12" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136100402</v>
       </c>
       <c r="B13" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136100365</v>
       </c>
       <c r="B14" t="n">
-        <v>92420</v>
+        <v>92426</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136100349</v>
       </c>
       <c r="B15" t="n">
-        <v>91076</v>
+        <v>91082</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136100358</v>
       </c>
       <c r="B16" t="n">
-        <v>91076</v>
+        <v>91082</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>136100354</v>
       </c>
       <c r="B18" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136100362</v>
       </c>
       <c r="B19" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136100366</v>
       </c>
       <c r="B20" t="n">
-        <v>93285</v>
+        <v>93291</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136100350</v>
       </c>
       <c r="B22" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>136100357</v>
       </c>
       <c r="B23" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>136100360</v>
       </c>
       <c r="B24" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136100370</v>
       </c>
       <c r="B25" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>136100371</v>
       </c>
       <c r="B26" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136100407</v>
       </c>
       <c r="B27" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>136100355</v>
       </c>
       <c r="B28" t="n">
-        <v>93369</v>
+        <v>93375</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>136100356</v>
       </c>
       <c r="B29" t="n">
-        <v>93369</v>
+        <v>93375</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>136100372</v>
       </c>
       <c r="B30" t="n">
-        <v>93369</v>
+        <v>93375</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>136100378</v>
       </c>
       <c r="B31" t="n">
-        <v>93369</v>
+        <v>93375</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>136100368</v>
       </c>
       <c r="B32" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>136100390</v>
       </c>
       <c r="B33" t="n">
-        <v>79469</v>
+        <v>79473</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>136100344</v>
       </c>
       <c r="B34" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>136100374</v>
       </c>
       <c r="B35" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>136100380</v>
       </c>
       <c r="B36" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>136100383</v>
       </c>
       <c r="B37" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>136100399</v>
       </c>
       <c r="B38" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>136100411</v>
       </c>
       <c r="B39" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         <v>136100343</v>
       </c>
       <c r="B40" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>136100347</v>
       </c>
       <c r="B41" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>136100352</v>
       </c>
       <c r="B42" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>136100364</v>
       </c>
       <c r="B43" t="n">
-        <v>80571</v>
+        <v>80575</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>136100345</v>
       </c>
       <c r="B44" t="n">
-        <v>78449</v>
+        <v>78453</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>136100391</v>
       </c>
       <c r="B45" t="n">
-        <v>78449</v>
+        <v>78453</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>136100384</v>
       </c>
       <c r="B46" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136100386</v>
       </c>
       <c r="B47" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>136100388</v>
       </c>
       <c r="B48" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>136100406</v>
       </c>
       <c r="B49" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>136100376</v>
       </c>
       <c r="B50" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>136100381</v>
       </c>
       <c r="B51" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>136100385</v>
       </c>
       <c r="B52" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>136100394</v>
       </c>
       <c r="B53" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>136100397</v>
       </c>
       <c r="B54" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>136100409</v>
       </c>
       <c r="B55" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>136100412</v>
       </c>
       <c r="B56" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>136100346</v>
       </c>
       <c r="B57" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>136100348</v>
       </c>
       <c r="B58" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>136100373</v>
       </c>
       <c r="B59" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>136100379</v>
       </c>
       <c r="B60" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>136100382</v>
       </c>
       <c r="B61" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>136100393</v>
       </c>
       <c r="B62" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>136100398</v>
       </c>
       <c r="B63" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         <v>136100413</v>
       </c>
       <c r="B64" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>136100414</v>
       </c>
       <c r="B65" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 33994-2026 artfynd.xlsx
+++ b/artfynd/A 33994-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136100389</v>
       </c>
       <c r="B2" t="n">
-        <v>97539</v>
+        <v>97540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136100396</v>
       </c>
       <c r="B3" t="n">
-        <v>92319</v>
+        <v>92320</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136100403</v>
       </c>
       <c r="B4" t="n">
-        <v>92319</v>
+        <v>92320</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136100351</v>
       </c>
       <c r="B5" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136100353</v>
       </c>
       <c r="B6" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136100361</v>
       </c>
       <c r="B7" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136100408</v>
       </c>
       <c r="B8" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136100377</v>
       </c>
       <c r="B9" t="n">
-        <v>81431</v>
+        <v>81432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136100363</v>
       </c>
       <c r="B10" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136100375</v>
       </c>
       <c r="B11" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136100400</v>
       </c>
       <c r="B12" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136100402</v>
       </c>
       <c r="B13" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136100365</v>
       </c>
       <c r="B14" t="n">
-        <v>92426</v>
+        <v>92427</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136100349</v>
       </c>
       <c r="B15" t="n">
-        <v>91082</v>
+        <v>91083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136100358</v>
       </c>
       <c r="B16" t="n">
-        <v>91082</v>
+        <v>91083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>136100354</v>
       </c>
       <c r="B18" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136100362</v>
       </c>
       <c r="B19" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136100366</v>
       </c>
       <c r="B20" t="n">
-        <v>93291</v>
+        <v>93292</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136100350</v>
       </c>
       <c r="B22" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>136100357</v>
       </c>
       <c r="B23" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>136100360</v>
       </c>
       <c r="B24" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136100370</v>
       </c>
       <c r="B25" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>136100371</v>
       </c>
       <c r="B26" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136100407</v>
       </c>
       <c r="B27" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>136100355</v>
       </c>
       <c r="B28" t="n">
-        <v>93375</v>
+        <v>93376</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>136100356</v>
       </c>
       <c r="B29" t="n">
-        <v>93375</v>
+        <v>93376</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>136100372</v>
       </c>
       <c r="B30" t="n">
-        <v>93375</v>
+        <v>93376</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>136100378</v>
       </c>
       <c r="B31" t="n">
-        <v>93375</v>
+        <v>93376</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>136100368</v>
       </c>
       <c r="B32" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>136100390</v>
       </c>
       <c r="B33" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>136100344</v>
       </c>
       <c r="B34" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>136100374</v>
       </c>
       <c r="B35" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>136100380</v>
       </c>
       <c r="B36" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>136100383</v>
       </c>
       <c r="B37" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>136100399</v>
       </c>
       <c r="B38" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>136100411</v>
       </c>
       <c r="B39" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         <v>136100343</v>
       </c>
       <c r="B40" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>136100347</v>
       </c>
       <c r="B41" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>136100352</v>
       </c>
       <c r="B42" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>136100364</v>
       </c>
       <c r="B43" t="n">
-        <v>80575</v>
+        <v>80576</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>136100345</v>
       </c>
       <c r="B44" t="n">
-        <v>78453</v>
+        <v>78454</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>136100391</v>
       </c>
       <c r="B45" t="n">
-        <v>78453</v>
+        <v>78454</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>136100384</v>
       </c>
       <c r="B46" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136100386</v>
       </c>
       <c r="B47" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>136100388</v>
       </c>
       <c r="B48" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>136100406</v>
       </c>
       <c r="B49" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>136100376</v>
       </c>
       <c r="B50" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>136100381</v>
       </c>
       <c r="B51" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>136100385</v>
       </c>
       <c r="B52" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>136100394</v>
       </c>
       <c r="B53" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>136100397</v>
       </c>
       <c r="B54" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>136100409</v>
       </c>
       <c r="B55" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>136100412</v>
       </c>
       <c r="B56" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>136100346</v>
       </c>
       <c r="B57" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>136100348</v>
       </c>
       <c r="B58" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>136100373</v>
       </c>
       <c r="B59" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>136100379</v>
       </c>
       <c r="B60" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>136100382</v>
       </c>
       <c r="B61" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>136100393</v>
       </c>
       <c r="B62" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>136100398</v>
       </c>
       <c r="B63" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         <v>136100413</v>
       </c>
       <c r="B64" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>136100414</v>
       </c>
       <c r="B65" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 33994-2026 artfynd.xlsx
+++ b/artfynd/A 33994-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136100389</v>
       </c>
       <c r="B2" t="n">
-        <v>97540</v>
+        <v>97551</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136100396</v>
       </c>
       <c r="B3" t="n">
-        <v>92320</v>
+        <v>92326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136100403</v>
       </c>
       <c r="B4" t="n">
-        <v>92320</v>
+        <v>92326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136100351</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136100353</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136100361</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136100408</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136100377</v>
       </c>
       <c r="B9" t="n">
-        <v>81432</v>
+        <v>81436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136100363</v>
       </c>
       <c r="B10" t="n">
-        <v>92253</v>
+        <v>92259</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136100375</v>
       </c>
       <c r="B11" t="n">
-        <v>92253</v>
+        <v>92259</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136100400</v>
       </c>
       <c r="B12" t="n">
-        <v>92253</v>
+        <v>92259</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136100402</v>
       </c>
       <c r="B13" t="n">
-        <v>92253</v>
+        <v>92259</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136100365</v>
       </c>
       <c r="B14" t="n">
-        <v>92427</v>
+        <v>92433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136100349</v>
       </c>
       <c r="B15" t="n">
-        <v>91083</v>
+        <v>91089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136100358</v>
       </c>
       <c r="B16" t="n">
-        <v>91083</v>
+        <v>91089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>136100354</v>
       </c>
       <c r="B18" t="n">
-        <v>92127</v>
+        <v>92133</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136100362</v>
       </c>
       <c r="B19" t="n">
-        <v>92127</v>
+        <v>92133</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136100366</v>
       </c>
       <c r="B20" t="n">
-        <v>93292</v>
+        <v>93298</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136100350</v>
       </c>
       <c r="B22" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>136100357</v>
       </c>
       <c r="B23" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>136100360</v>
       </c>
       <c r="B24" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136100370</v>
       </c>
       <c r="B25" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>136100371</v>
       </c>
       <c r="B26" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136100407</v>
       </c>
       <c r="B27" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>136100355</v>
       </c>
       <c r="B28" t="n">
-        <v>93376</v>
+        <v>93382</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>136100356</v>
       </c>
       <c r="B29" t="n">
-        <v>93376</v>
+        <v>93382</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>136100372</v>
       </c>
       <c r="B30" t="n">
-        <v>93376</v>
+        <v>93382</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>136100378</v>
       </c>
       <c r="B31" t="n">
-        <v>93376</v>
+        <v>93382</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>136100368</v>
       </c>
       <c r="B32" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>136100390</v>
       </c>
       <c r="B33" t="n">
-        <v>79474</v>
+        <v>79478</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>136100344</v>
       </c>
       <c r="B34" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>136100374</v>
       </c>
       <c r="B35" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>136100380</v>
       </c>
       <c r="B36" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>136100383</v>
       </c>
       <c r="B37" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>136100399</v>
       </c>
       <c r="B38" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>136100411</v>
       </c>
       <c r="B39" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         <v>136100343</v>
       </c>
       <c r="B40" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>136100347</v>
       </c>
       <c r="B41" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>136100352</v>
       </c>
       <c r="B42" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>136100364</v>
       </c>
       <c r="B43" t="n">
-        <v>80576</v>
+        <v>80580</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>136100345</v>
       </c>
       <c r="B44" t="n">
-        <v>78454</v>
+        <v>78458</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>136100391</v>
       </c>
       <c r="B45" t="n">
-        <v>78454</v>
+        <v>78458</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136100386</v>
       </c>
       <c r="B47" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>136100388</v>
       </c>
       <c r="B48" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>136100406</v>
       </c>
       <c r="B49" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>136100376</v>
       </c>
       <c r="B50" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>136100381</v>
       </c>
       <c r="B51" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>136100385</v>
       </c>
       <c r="B52" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>136100394</v>
       </c>
       <c r="B53" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>136100397</v>
       </c>
       <c r="B54" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>136100409</v>
       </c>
       <c r="B55" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>136100412</v>
       </c>
       <c r="B56" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>136100346</v>
       </c>
       <c r="B57" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>136100348</v>
       </c>
       <c r="B58" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>136100373</v>
       </c>
       <c r="B59" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>136100379</v>
       </c>
       <c r="B60" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>136100382</v>
       </c>
       <c r="B61" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>136100393</v>
       </c>
       <c r="B62" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>136100398</v>
       </c>
       <c r="B63" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         <v>136100413</v>
       </c>
       <c r="B64" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>136100414</v>
       </c>
       <c r="B65" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 33994-2026 artfynd.xlsx
+++ b/artfynd/A 33994-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136100389</v>
       </c>
       <c r="B2" t="n">
-        <v>97551</v>
+        <v>97564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136100396</v>
       </c>
       <c r="B3" t="n">
-        <v>92326</v>
+        <v>92333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136100403</v>
       </c>
       <c r="B4" t="n">
-        <v>92326</v>
+        <v>92333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136100351</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136100353</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136100361</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136100408</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136100377</v>
       </c>
       <c r="B9" t="n">
-        <v>81436</v>
+        <v>81442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136100363</v>
       </c>
       <c r="B10" t="n">
-        <v>92259</v>
+        <v>92266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136100375</v>
       </c>
       <c r="B11" t="n">
-        <v>92259</v>
+        <v>92266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136100400</v>
       </c>
       <c r="B12" t="n">
-        <v>92259</v>
+        <v>92266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136100402</v>
       </c>
       <c r="B13" t="n">
-        <v>92259</v>
+        <v>92266</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136100365</v>
       </c>
       <c r="B14" t="n">
-        <v>92433</v>
+        <v>92440</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136100349</v>
       </c>
       <c r="B15" t="n">
-        <v>91089</v>
+        <v>91096</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136100358</v>
       </c>
       <c r="B16" t="n">
-        <v>91089</v>
+        <v>91096</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>136100354</v>
       </c>
       <c r="B18" t="n">
-        <v>92133</v>
+        <v>92140</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136100362</v>
       </c>
       <c r="B19" t="n">
-        <v>92133</v>
+        <v>92140</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136100366</v>
       </c>
       <c r="B20" t="n">
-        <v>93298</v>
+        <v>93305</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136100350</v>
       </c>
       <c r="B22" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>136100357</v>
       </c>
       <c r="B23" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>136100360</v>
       </c>
       <c r="B24" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136100370</v>
       </c>
       <c r="B25" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>136100371</v>
       </c>
       <c r="B26" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136100407</v>
       </c>
       <c r="B27" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>136100355</v>
       </c>
       <c r="B28" t="n">
-        <v>93382</v>
+        <v>93389</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>136100356</v>
       </c>
       <c r="B29" t="n">
-        <v>93382</v>
+        <v>93389</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>136100372</v>
       </c>
       <c r="B30" t="n">
-        <v>93382</v>
+        <v>93389</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>136100378</v>
       </c>
       <c r="B31" t="n">
-        <v>93382</v>
+        <v>93389</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>136100368</v>
       </c>
       <c r="B32" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>136100390</v>
       </c>
       <c r="B33" t="n">
-        <v>79478</v>
+        <v>79484</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>136100344</v>
       </c>
       <c r="B34" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>136100374</v>
       </c>
       <c r="B35" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>136100380</v>
       </c>
       <c r="B36" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>136100383</v>
       </c>
       <c r="B37" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>136100399</v>
       </c>
       <c r="B38" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>136100411</v>
       </c>
       <c r="B39" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         <v>136100343</v>
       </c>
       <c r="B40" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>136100347</v>
       </c>
       <c r="B41" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>136100352</v>
       </c>
       <c r="B42" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>136100364</v>
       </c>
       <c r="B43" t="n">
-        <v>80580</v>
+        <v>80586</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>136100345</v>
       </c>
       <c r="B44" t="n">
-        <v>78458</v>
+        <v>78464</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>136100391</v>
       </c>
       <c r="B45" t="n">
-        <v>78458</v>
+        <v>78464</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>136100384</v>
       </c>
       <c r="B46" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136100386</v>
       </c>
       <c r="B47" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>136100388</v>
       </c>
       <c r="B48" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>136100406</v>
       </c>
       <c r="B49" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>136100376</v>
       </c>
       <c r="B50" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>136100381</v>
       </c>
       <c r="B51" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>136100385</v>
       </c>
       <c r="B52" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>136100394</v>
       </c>
       <c r="B53" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>136100397</v>
       </c>
       <c r="B54" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>136100409</v>
       </c>
       <c r="B55" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>136100412</v>
       </c>
       <c r="B56" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>136100346</v>
       </c>
       <c r="B57" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>136100348</v>
       </c>
       <c r="B58" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>136100373</v>
       </c>
       <c r="B59" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>136100379</v>
       </c>
       <c r="B60" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>136100382</v>
       </c>
       <c r="B61" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>136100393</v>
       </c>
       <c r="B62" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>136100398</v>
       </c>
       <c r="B63" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         <v>136100413</v>
       </c>
       <c r="B64" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>136100414</v>
       </c>
       <c r="B65" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 33994-2026 artfynd.xlsx
+++ b/artfynd/A 33994-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136100389</v>
       </c>
       <c r="B2" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136100396</v>
       </c>
       <c r="B3" t="n">
-        <v>92333</v>
+        <v>92334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136100403</v>
       </c>
       <c r="B4" t="n">
-        <v>92333</v>
+        <v>92334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136100363</v>
       </c>
       <c r="B10" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136100375</v>
       </c>
       <c r="B11" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136100400</v>
       </c>
       <c r="B12" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136100402</v>
       </c>
       <c r="B13" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136100365</v>
       </c>
       <c r="B14" t="n">
-        <v>92440</v>
+        <v>92441</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136100349</v>
       </c>
       <c r="B15" t="n">
-        <v>91096</v>
+        <v>91097</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136100358</v>
       </c>
       <c r="B16" t="n">
-        <v>91096</v>
+        <v>91097</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>136100354</v>
       </c>
       <c r="B18" t="n">
-        <v>92140</v>
+        <v>92141</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136100362</v>
       </c>
       <c r="B19" t="n">
-        <v>92140</v>
+        <v>92141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136100366</v>
       </c>
       <c r="B20" t="n">
-        <v>93305</v>
+        <v>93306</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136100350</v>
       </c>
       <c r="B22" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>136100357</v>
       </c>
       <c r="B23" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>136100360</v>
       </c>
       <c r="B24" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136100370</v>
       </c>
       <c r="B25" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>136100371</v>
       </c>
       <c r="B26" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136100407</v>
       </c>
       <c r="B27" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>136100355</v>
       </c>
       <c r="B28" t="n">
-        <v>93389</v>
+        <v>93390</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>136100356</v>
       </c>
       <c r="B29" t="n">
-        <v>93389</v>
+        <v>93390</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>136100372</v>
       </c>
       <c r="B30" t="n">
-        <v>93389</v>
+        <v>93390</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>136100378</v>
       </c>
       <c r="B31" t="n">
-        <v>93389</v>
+        <v>93390</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136100386</v>
       </c>
       <c r="B47" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>136100388</v>
       </c>
       <c r="B48" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>136100406</v>
       </c>
       <c r="B49" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 33994-2026 artfynd.xlsx
+++ b/artfynd/A 33994-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136100389</v>
       </c>
       <c r="B2" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136100396</v>
       </c>
       <c r="B3" t="n">
-        <v>92334</v>
+        <v>92347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136100403</v>
       </c>
       <c r="B4" t="n">
-        <v>92334</v>
+        <v>92347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136100351</v>
       </c>
       <c r="B5" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136100353</v>
       </c>
       <c r="B6" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136100361</v>
       </c>
       <c r="B7" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136100408</v>
       </c>
       <c r="B8" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136100377</v>
       </c>
       <c r="B9" t="n">
-        <v>81442</v>
+        <v>81455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136100363</v>
       </c>
       <c r="B10" t="n">
-        <v>92267</v>
+        <v>92280</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136100375</v>
       </c>
       <c r="B11" t="n">
-        <v>92267</v>
+        <v>92280</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136100400</v>
       </c>
       <c r="B12" t="n">
-        <v>92267</v>
+        <v>92280</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136100402</v>
       </c>
       <c r="B13" t="n">
-        <v>92267</v>
+        <v>92280</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136100365</v>
       </c>
       <c r="B14" t="n">
-        <v>92441</v>
+        <v>92454</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136100349</v>
       </c>
       <c r="B15" t="n">
-        <v>91097</v>
+        <v>91110</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136100358</v>
       </c>
       <c r="B16" t="n">
-        <v>91097</v>
+        <v>91110</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>136100354</v>
       </c>
       <c r="B18" t="n">
-        <v>92141</v>
+        <v>92154</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136100362</v>
       </c>
       <c r="B19" t="n">
-        <v>92141</v>
+        <v>92154</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136100366</v>
       </c>
       <c r="B20" t="n">
-        <v>93306</v>
+        <v>93319</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136100350</v>
       </c>
       <c r="B22" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>136100357</v>
       </c>
       <c r="B23" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>136100360</v>
       </c>
       <c r="B24" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136100370</v>
       </c>
       <c r="B25" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>136100371</v>
       </c>
       <c r="B26" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136100407</v>
       </c>
       <c r="B27" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>136100355</v>
       </c>
       <c r="B28" t="n">
-        <v>93390</v>
+        <v>93403</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>136100356</v>
       </c>
       <c r="B29" t="n">
-        <v>93390</v>
+        <v>93403</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>136100372</v>
       </c>
       <c r="B30" t="n">
-        <v>93390</v>
+        <v>93403</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>136100378</v>
       </c>
       <c r="B31" t="n">
-        <v>93390</v>
+        <v>93403</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>136100368</v>
       </c>
       <c r="B32" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>136100390</v>
       </c>
       <c r="B33" t="n">
-        <v>79484</v>
+        <v>79497</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>136100344</v>
       </c>
       <c r="B34" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>136100374</v>
       </c>
       <c r="B35" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>136100380</v>
       </c>
       <c r="B36" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>136100383</v>
       </c>
       <c r="B37" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>136100399</v>
       </c>
       <c r="B38" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>136100411</v>
       </c>
       <c r="B39" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         <v>136100343</v>
       </c>
       <c r="B40" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>136100347</v>
       </c>
       <c r="B41" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>136100352</v>
       </c>
       <c r="B42" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>136100364</v>
       </c>
       <c r="B43" t="n">
-        <v>80586</v>
+        <v>80599</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>136100345</v>
       </c>
       <c r="B44" t="n">
-        <v>78464</v>
+        <v>78477</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>136100391</v>
       </c>
       <c r="B45" t="n">
-        <v>78464</v>
+        <v>78477</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>136100384</v>
       </c>
       <c r="B46" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136100386</v>
       </c>
       <c r="B47" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>136100388</v>
       </c>
       <c r="B48" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>136100406</v>
       </c>
       <c r="B49" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>136100376</v>
       </c>
       <c r="B50" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>136100381</v>
       </c>
       <c r="B51" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>136100385</v>
       </c>
       <c r="B52" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>136100394</v>
       </c>
       <c r="B53" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>136100397</v>
       </c>
       <c r="B54" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>136100409</v>
       </c>
       <c r="B55" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>136100412</v>
       </c>
       <c r="B56" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>136100346</v>
       </c>
       <c r="B57" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>136100348</v>
       </c>
       <c r="B58" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>136100373</v>
       </c>
       <c r="B59" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>136100379</v>
       </c>
       <c r="B60" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>136100382</v>
       </c>
       <c r="B61" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>136100393</v>
       </c>
       <c r="B62" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>136100398</v>
       </c>
       <c r="B63" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         <v>136100413</v>
       </c>
       <c r="B64" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>136100414</v>
       </c>
       <c r="B65" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 33994-2026 artfynd.xlsx
+++ b/artfynd/A 33994-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136100389</v>
       </c>
       <c r="B2" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136100396</v>
       </c>
       <c r="B3" t="n">
-        <v>92347</v>
+        <v>92348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136100403</v>
       </c>
       <c r="B4" t="n">
-        <v>92347</v>
+        <v>92348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136100351</v>
       </c>
       <c r="B5" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136100353</v>
       </c>
       <c r="B6" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136100361</v>
       </c>
       <c r="B7" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136100408</v>
       </c>
       <c r="B8" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136100377</v>
       </c>
       <c r="B9" t="n">
-        <v>81455</v>
+        <v>81456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136100363</v>
       </c>
       <c r="B10" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136100375</v>
       </c>
       <c r="B11" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136100400</v>
       </c>
       <c r="B12" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136100402</v>
       </c>
       <c r="B13" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136100365</v>
       </c>
       <c r="B14" t="n">
-        <v>92454</v>
+        <v>92455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>136100349</v>
       </c>
       <c r="B15" t="n">
-        <v>91110</v>
+        <v>91111</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>136100358</v>
       </c>
       <c r="B16" t="n">
-        <v>91110</v>
+        <v>91111</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>136100354</v>
       </c>
       <c r="B18" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>136100362</v>
       </c>
       <c r="B19" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>136100366</v>
       </c>
       <c r="B20" t="n">
-        <v>93319</v>
+        <v>93320</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136100350</v>
       </c>
       <c r="B22" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>136100357</v>
       </c>
       <c r="B23" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>136100360</v>
       </c>
       <c r="B24" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136100370</v>
       </c>
       <c r="B25" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>136100371</v>
       </c>
       <c r="B26" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136100407</v>
       </c>
       <c r="B27" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>136100355</v>
       </c>
       <c r="B28" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>136100356</v>
       </c>
       <c r="B29" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>136100372</v>
       </c>
       <c r="B30" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>136100378</v>
       </c>
       <c r="B31" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>136100368</v>
       </c>
       <c r="B32" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>136100390</v>
       </c>
       <c r="B33" t="n">
-        <v>79497</v>
+        <v>79498</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>136100344</v>
       </c>
       <c r="B34" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>136100374</v>
       </c>
       <c r="B35" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>136100380</v>
       </c>
       <c r="B36" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>136100383</v>
       </c>
       <c r="B37" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>136100399</v>
       </c>
       <c r="B38" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>136100411</v>
       </c>
       <c r="B39" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         <v>136100343</v>
       </c>
       <c r="B40" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>136100347</v>
       </c>
       <c r="B41" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>136100352</v>
       </c>
       <c r="B42" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>136100364</v>
       </c>
       <c r="B43" t="n">
-        <v>80599</v>
+        <v>80600</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>136100345</v>
       </c>
       <c r="B44" t="n">
-        <v>78477</v>
+        <v>78478</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>136100391</v>
       </c>
       <c r="B45" t="n">
-        <v>78477</v>
+        <v>78478</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136100386</v>
       </c>
       <c r="B47" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>136100388</v>
       </c>
       <c r="B48" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>136100406</v>
       </c>
       <c r="B49" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>136100376</v>
       </c>
       <c r="B50" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>136100381</v>
       </c>
       <c r="B51" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>136100385</v>
       </c>
       <c r="B52" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>136100394</v>
       </c>
       <c r="B53" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>136100397</v>
       </c>
       <c r="B54" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>136100409</v>
       </c>
       <c r="B55" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>136100412</v>
       </c>
       <c r="B56" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>136100346</v>
       </c>
       <c r="B57" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>136100348</v>
       </c>
       <c r="B58" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>136100373</v>
       </c>
       <c r="B59" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>136100379</v>
       </c>
       <c r="B60" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>136100382</v>
       </c>
       <c r="B61" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>136100393</v>
       </c>
       <c r="B62" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>136100398</v>
       </c>
       <c r="B63" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         <v>136100413</v>
       </c>
       <c r="B64" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>136100414</v>
       </c>
       <c r="B65" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
